--- a/Assessment Questions/AIE/BDF-117/HDFS AND MAP REDUCE/HDFS – Big Data Storage/HDFS – Big Data Storage.xlsx
+++ b/Assessment Questions/AIE/BDF-117/HDFS AND MAP REDUCE/HDFS – Big Data Storage/HDFS – Big Data Storage.xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Block_ID,File_Name,File_Size_MB,Block_Size_MB,Block_Count,Replication_Factor,NameNode_ID,DataNode_ID,Rack_ID,Storage_Type,Disk_Usage_Pct,Read_Throughput_MBps,Write_Throughput_MBps,Read_Latency_Ms,Write_Latency_Ms,Metadata_Size_KB,Heartbeat_Status,Block_Location,Data_Locality_Score,Replication_Status,Corrupt_Blocks,Pending_Replication,Under_Replicated,Over_Replicated,Balancer_Score,Cluster_Health_Pct</t>
-  </si>
-  <si>
-    <t>BLK-001,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-01,Rack-1,SSD,45,450,320,12,18,64,Healthy,Rack-1,92,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-002,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-05,Rack-2,HDD,62,280,210,28,35,64,Healthy,Rack-2,88,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-003,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-09,Rack-3,SSD,38,480,350,10,15,64,Healthy,Rack-3,94,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-004,sales_transactions.avro,512,128,4,3,NN-01,DN-02,Rack-1,HDD,58,310,240,24,32,32,Healthy,Rack-1,89,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-005,sales_transactions.avro,512,128,4,3,NN-01,DN-06,Rack-2,SSD,42,420,340,14,20,32,Healthy,Rack-2,91,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-006,sales_transactions.avro,512,128,4,3,NN-01,DN-10,Rack-3,HDD,55,295,225,26,34,32,Healthy,Rack-3,87,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-007,customer_data.orc,2048,128,16,3,NN-01,DN-03,Rack-1,SSD,52,510,390,9,14,128,Healthy,Rack-1,95,OK,0,0,0,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-008,customer_data.orc,2048,128,16,3,NN-01,DN-07,Rack-2,HDD,68,265,195,32,42,128,Healthy,Rack-2,84,OK,0,1,1,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-009,customer_data.orc,2048,128,16,3,NN-01,DN-11,Rack-3,SSD,48,495,380,11,16,128,Healthy,Rack-3,93,OK,0,0,0,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-010,clickstream.json,4096,128,32,3,NN-01,DN-04,Rack-1,HDD,72,235,180,38,48,256,Healthy,Rack-1,82,Under,0,2,2,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-011,clickstream.json,4096,128,32,3,NN-01,DN-08,Rack-2,SSD,48,460,360,13,19,256,Healthy,Rack-2,90,OK,0,0,0,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-012,clickstream.json,4096,128,32,3,NN-01,DN-12,Rack-3,HDD,65,275,205,30,38,256,Healthy,Rack-3,86,OK,0,0,0,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-013,product_catalog.csv,128,128,1,3,NN-01,DN-01,Rack-1,SSD,45,490,380,8,12,8,Healthy,Rack-1,96,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-014,product_catalog.csv,128,128,1,3,NN-01,DN-05,Rack-2,HDD,62,305,235,26,33,8,Healthy,Rack-2,89,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-015,product_catalog.csv,128,128,1,3,NN-01,DN-09,Rack-3,SSD,38,485,375,9,13,8,Healthy,Rack-3,95,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-016,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-02,Rack-1,HDD,75,210,165,42,55,512,Healthy,Rack-1,80,Under,1,3,3,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-017,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-06,Rack-2,SSD,55,435,345,15,22,512,Healthy,Rack-2,88,OK,0,0,0,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-018,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-10,Rack-3,HDD,68,250,190,35,45,512,Healthy,Rack-3,82,OK,0,0,0,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-019,weblogs_2024.avro,3072,128,24,3,NN-01,DN-03,Rack-1,SSD,48,470,355,12,17,192,Healthy,Rack-1,92,OK,0,0,0,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-020,weblogs_2024.avro,3072,128,24,3,NN-01,DN-07,Rack-2,HDD,70,245,185,36,46,192,Healthy,Rack-2,83,OK,0,1,1,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-021,weblogs_2024.avro,3072,128,24,3,NN-01,DN-11,Rack-3,SSD,50,455,360,13,18,192,Healthy,Rack-3,91,OK,0,0,0,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-022,financial_transactions.parquet,6144,128,48,3,NN-01,DN-04,Rack-1,HDD,78,195,150,48,62,384,Healthy,Rack-1,78,Under,2,5,5,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-023,financial_transactions.parquet,6144,128,48,3,NN-01,DN-08,Rack-2,SSD,52,425,330,16,24,384,Healthy,Rack-2,87,OK,0,0,0,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-024,financial_transactions.parquet,6144,128,48,3,NN-01,DN-12,Rack-3,HDD,72,230,175,40,52,384,Healthy,Rack-3,81,OK,0,0,0,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-025,image_data.bin,5120,128,40,3,NN-01,DN-01,Rack-1,SSD,48,485,370,10,15,320,Healthy,Rack-1,94,OK,0,0,0,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-026,image_data.bin,5120,128,40,3,NN-01,DN-05,Rack-2,HDD,65,285,215,29,37,320,Healthy,Rack-2,86,OK,0,1,1,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-027,image_data.bin,5120,128,40,3,NN-01,DN-09,Rack-3,SSD,42,475,365,11,16,320,Healthy,Rack-3,93,OK,0,0,0,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-028,backup_data.parquet,10240,128,80,3,NN-01,DN-02,Rack-1,HDD,82,180,140,55,72,640,Healthy,Rack-1,75,Under,3,7,7,0,60,86</t>
-  </si>
-  <si>
-    <t>BLK-029,backup_data.parquet,10240,128,80,3,NN-01,DN-06,Rack-2,SSD,58,415,310,18,26,640,Healthy,Rack-2,85,OK,0,0,0,0,60,86</t>
-  </si>
-  <si>
-    <t>BLK-030,backup_data.parquet,10240,128,80,3,NN-01,DN-10,Rack-3,HDD,75,210,160,45,58,640,Healthy,Rack-3,79,OK,0,0,0,0,60,86</t>
-  </si>
-  <si>
-    <t>Q.No,Question,HDFS_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is HDFS (Hadoop Distributed File System)? Explain its core architecture using the dataset.","HDFS Architecture","Analyze NameNode, DataNode, Block structure","HDFS has NameNode (metadata) and DataNodes (data storage). Files split into 128MB blocks, replicated across DataNodes","HDFS provides distributed, fault-tolerant storage for Big Data"</t>
-  </si>
-  <si>
-    <t>2,"What is the default block size in HDFS? Why is 128MB used? Calculate total blocks from dataset.","HDFS Block Size","Analyze Block_Size_MB, Block_Count","Default block size: 128MB. Total blocks: 384 across all files. Large blocks reduce metadata overhead and improve throughput","Large block size minimizes NameNode memory usage and improves sequential I/O"</t>
-  </si>
-  <si>
-    <t>3,"What is data replication in HDFS? Why is replication factor 3 used? Calculate storage overhead.","Data Replication","Analyze Replication_Factor, File_Size_MB","Replication factor: 3. Total raw data: 34,816 MB; Actual storage: 104,448 MB (3x overhead). Provides fault tolerance","Replication ensures data durability - if one node fails, data available on 2 others"</t>
-  </si>
-  <si>
-    <t>4,"What is the role of NameNode in HDFS? Analyze NameNode metrics from the dataset.","NameNode Role","Analyze NameNode_ID, Metadata_Size_KB","NameNode (NN-01) manages metadata: stores file-to-block mapping. Metadata size: 8-640 KB per file. Tracks block locations","NameNode is the master node - stores metadata, not actual data"</t>
-  </si>
-  <si>
-    <t>5,"What is the role of DataNode in HDFS? Analyze DataNode distribution and storage types.","DataNode Role","Analyze DataNode_ID, Storage_Type, Disk_Usage_Pct","DataNodes: DN-01 to DN-12 across 3 racks. Storage: SSD (45% usage, 48% avg) and HDD (68% usage, 58% avg)","DataNodes store actual data blocks and report to NameNode"</t>
-  </si>
-  <si>
-    <t>6,"What is rack awareness in HDFS? How does it improve data locality?","Rack Awareness","Analyze Rack_ID, Data_Locality_Score","3 racks (Rack-1,2,3). Data locality scores: 92-96 for local reads, 78-84 for remote. Rack awareness reduces cross-rack traffic","Rack awareness places replicas across racks to prevent rack failure from causing data loss"</t>
-  </si>
-  <si>
-    <t>7,"What is the difference between SSD and HDD storage in HDFS? Compare performance metrics.","Storage Performance","Compare SSD vs HDD performance metrics","SSD: Read 450-510 MBps, Write 350-390 MBps, Latency 8-18ms; HDD: Read 195-310 MBps, Write 140-240 MBps, Latency 24-72ms","SSD provides 2-3x faster performance for hot data; HDD for cold storage"</t>
-  </si>
-  <si>
-    <t>8,"What is data locality? Calculate the data locality score for different file types.","Data Locality","Analyze Data_Locality_Score by file type","Customer data: 95, Product catalog: 96, User logs: 92, Sensor data: 80-88, Financial: 78-87. Larger files have lower locality","Data locality improves performance by moving computation to data"</t>
-  </si>
-  <si>
-    <t>9,"What is block corruption in HDFS? Identify files with corrupt blocks.","Block Corruption","Filter Corrupt_Blocks &gt; 0","Financial transactions: 2 corrupt blocks; Backup data: 3 corrupt blocks; Sensor data: 1 corrupt block. Total: 6 corrupt blocks","HDFS automatically detects and replicates corrupt blocks"</t>
-  </si>
-  <si>
-    <t>10,"What are under-replicated blocks? Identify files with replication issues.","Replication Management","Analyze Under_Replicated, Replication_Status","Clickstream: 2 under-replicated; Sensor data: 3; Financial: 5; Backup: 7. Total: 17 under-replicated blocks","HDFS automatically re-replicates under-replicated blocks to maintain replication factor"</t>
-  </si>
-  <si>
-    <t>11,"What is the HDFS balancer? Analyze the balancer score for different files.","Load Balancing","Analyze Balancer_Score, Disk_Usage_Pct","Balancer scores: 85-90 for balanced files; 60-70 for unbalanced. Files with high disk usage (75-82%) have lower balancer scores","Balancer redistributes data to ensure even cluster utilization"</t>
-  </si>
-  <si>
-    <t>12,"What is the relationship between file size and read throughput? Analyze performance scaling.","Performance Analysis","Correlate File_Size_MB with Read_Throughput_MBps","Small files (128MB): 490 MBps; Medium (512MB): 310-420 MBps; Large (8192MB): 210-435 MBps. Larger files have more variable performance","Performance depends on data distribution and storage type"</t>
-  </si>
-  <si>
-    <t>13,"What is the cluster health percentage? Calculate average health by storage type.","Cluster Health","Group by Storage_Type; average Cluster_Health_Pct","SSD clusters: 97.8% health; HDD clusters: 93.2% health. Overall cluster health: 95.2%","Regular monitoring and balancing maintain cluster health"</t>
-  </si>
-  <si>
-    <t>14,"What is the difference between read and write latency? Compare across storage types.","Latency Analysis","Compare Read_Latency_Ms vs Write_Latency_Ms","SSD: Read 8-16ms, Write 12-26ms; HDD: Read 24-55ms, Write 32-72ms. Write latency 30-40% higher than read","Write operations require additional overhead for replication"</t>
-  </si>
-  <si>
-    <t>15,"What is the HDFS architecture for large files? Analyze the 10GB backup file.","Large File Handling","Analyze backup_data.parquet (10,240 MB)","Blocks: 80 blocks × 128MB; Replication: 3; Storage: 30,720 MB actual; Under-replicated: 7 blocks; Health: 86%","Large files are split into many blocks distributed across cluster"</t>
-  </si>
-  <si>
-    <t>16,"What is the NameNode metadata size? Calculate metadata overhead for different file sizes.","Metadata Overhead","Analyze File_Size_MB vs Metadata_Size_KB","Small file (128MB): 8KB metadata; Large file (10GB): 640KB metadata. Overhead: ~64 bytes per block","NameNode memory limits number of files; each file/block consumes memory"</t>
-  </si>
-  <si>
-    <t>17,"What are the different storage types used in HDFS? Identify files by storage type.","Storage Tiering","Group by Storage_Type, count files","SSD: 15 files (50%): user_logs, customer_data, weblogs, product_catalog; HDD: 15 files (50%): sales, clickstream, sensor, financial, backup","Hot data on SSD, cold data on HDD for cost-performance balance"</t>
-  </si>
-  <si>
-    <t>18,"What is the replication status of files? Identify files with replication issues.","Replication Status","Analyze Replication_Status, Under_Replicated","OK: 24 files (80%); Under: 6 files (20%). Clickstream, sensor, financial, backup have under-replicated blocks","Replication issues require attention to maintain fault tolerance"</t>
-  </si>
-  <si>
-    <t>19,"What is the HDFS read and write throughput? Calculate average throughput by storage type.","Throughput Analysis","Group by Storage_Type; average Read/Write Throughput","SSD: Read 475 MBps, Write 365 MBps; HDD: Read 255 MBps, Write 190 MBps. SSD is 1.9x faster","Storage type selection impacts analytics performance"</t>
-  </si>
-  <si>
-    <t>20,"Create an HDFS cluster summary with key metrics: total storage, used storage, replication overhead, cluster health.","Cluster Summary","Calculate summary metrics","Total Raw: 34,816 MB; Actual Storage: 104,448 MB (3x replication); Used: 62,669 MB (60%); Overhead: 69,632 MB; Health: 95.2%","HDFS provides scalable, fault-tolerant storage with replication overhead"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,983 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Block_ID,File_Name,File_Size_MB,Block_Size_MB,Block_Count,Replication_Factor,NameNode_ID,DataNode_ID,Rack_ID,Storage_Type,Disk_Usage_Pct,Read_Throughput_MBps,Write_Throughput_MBps,Read_Latency_Ms,Write_Latency_Ms,Metadata_Size_KB,Heartbeat_Status,Block_Location,Data_Locality_Score,Replication_Status,Corrupt_Blocks,Pending_Replication,Under_Replicated,Over_Replicated,Balancer_Score,Cluster_Health_Pct</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>BLK-001,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-01,Rack-1,SSD,45,450,320,12,18,64,Healthy,Rack-1,92,OK,0,0,0,0,85,98</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BLK-002,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-05,Rack-2,HDD,62,280,210,28,35,64,Healthy,Rack-2,88,OK,0,0,0,0,85,98</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BLK-003,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-09,Rack-3,SSD,38,480,350,10,15,64,Healthy,Rack-3,94,OK,0,0,0,0,85,98</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BLK-004,sales_transactions.avro,512,128,4,3,NN-01,DN-02,Rack-1,HDD,58,310,240,24,32,32,Healthy,Rack-1,89,OK,0,0,0,0,82,97</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BLK-005,sales_transactions.avro,512,128,4,3,NN-01,DN-06,Rack-2,SSD,42,420,340,14,20,32,Healthy,Rack-2,91,OK,0,0,0,0,82,97</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BLK-006,sales_transactions.avro,512,128,4,3,NN-01,DN-10,Rack-3,HDD,55,295,225,26,34,32,Healthy,Rack-3,87,OK,0,0,0,0,82,97</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>BLK-007,customer_data.orc,2048,128,16,3,NN-01,DN-03,Rack-1,SSD,52,510,390,9,14,128,Healthy,Rack-1,95,OK,0,0,0,0,88,99</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BLK-008,customer_data.orc,2048,128,16,3,NN-01,DN-07,Rack-2,HDD,68,265,195,32,42,128,Healthy,Rack-2,84,OK,0,1,1,0,88,99</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BLK-009,customer_data.orc,2048,128,16,3,NN-01,DN-11,Rack-3,SSD,48,495,380,11,16,128,Healthy,Rack-3,93,OK,0,0,0,0,88,99</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>BLK-010,clickstream.json,4096,128,32,3,NN-01,DN-04,Rack-1,HDD,72,235,180,38,48,256,Healthy,Rack-1,82,Under,0,2,2,0,75,94</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>BLK-011,clickstream.json,4096,128,32,3,NN-01,DN-08,Rack-2,SSD,48,460,360,13,19,256,Healthy,Rack-2,90,OK,0,0,0,0,75,94</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>BLK-012,clickstream.json,4096,128,32,3,NN-01,DN-12,Rack-3,HDD,65,275,205,30,38,256,Healthy,Rack-3,86,OK,0,0,0,0,75,94</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>BLK-013,product_catalog.csv,128,128,1,3,NN-01,DN-01,Rack-1,SSD,45,490,380,8,12,8,Healthy,Rack-1,96,OK,0,0,0,0,90,99</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>BLK-014,product_catalog.csv,128,128,1,3,NN-01,DN-05,Rack-2,HDD,62,305,235,26,33,8,Healthy,Rack-2,89,OK,0,0,0,0,90,99</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BLK-015,product_catalog.csv,128,128,1,3,NN-01,DN-09,Rack-3,SSD,38,485,375,9,13,8,Healthy,Rack-3,95,OK,0,0,0,0,90,99</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>BLK-016,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-02,Rack-1,HDD,75,210,165,42,55,512,Healthy,Rack-1,80,Under,1,3,3,0,70,91</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>BLK-017,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-06,Rack-2,SSD,55,435,345,15,22,512,Healthy,Rack-2,88,OK,0,0,0,0,70,91</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>BLK-018,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-10,Rack-3,HDD,68,250,190,35,45,512,Healthy,Rack-3,82,OK,0,0,0,0,70,91</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>BLK-019,weblogs_2024.avro,3072,128,24,3,NN-01,DN-03,Rack-1,SSD,48,470,355,12,17,192,Healthy,Rack-1,92,OK,0,0,0,0,80,96</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>BLK-020,weblogs_2024.avro,3072,128,24,3,NN-01,DN-07,Rack-2,HDD,70,245,185,36,46,192,Healthy,Rack-2,83,OK,0,1,1,0,80,96</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>BLK-021,weblogs_2024.avro,3072,128,24,3,NN-01,DN-11,Rack-3,SSD,50,455,360,13,18,192,Healthy,Rack-3,91,OK,0,0,0,0,80,96</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>BLK-022,financial_transactions.parquet,6144,128,48,3,NN-01,DN-04,Rack-1,HDD,78,195,150,48,62,384,Healthy,Rack-1,78,Under,2,5,5,0,65,89</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>BLK-023,financial_transactions.parquet,6144,128,48,3,NN-01,DN-08,Rack-2,SSD,52,425,330,16,24,384,Healthy,Rack-2,87,OK,0,0,0,0,65,89</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>BLK-024,financial_transactions.parquet,6144,128,48,3,NN-01,DN-12,Rack-3,HDD,72,230,175,40,52,384,Healthy,Rack-3,81,OK,0,0,0,0,65,89</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>BLK-025,image_data.bin,5120,128,40,3,NN-01,DN-01,Rack-1,SSD,48,485,370,10,15,320,Healthy,Rack-1,94,OK,0,0,0,0,85,97</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>BLK-026,image_data.bin,5120,128,40,3,NN-01,DN-05,Rack-2,HDD,65,285,215,29,37,320,Healthy,Rack-2,86,OK,0,1,1,0,85,97</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>BLK-027,image_data.bin,5120,128,40,3,NN-01,DN-09,Rack-3,SSD,42,475,365,11,16,320,Healthy,Rack-3,93,OK,0,0,0,0,85,97</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>BLK-028,backup_data.parquet,10240,128,80,3,NN-01,DN-02,Rack-1,HDD,82,180,140,55,72,640,Healthy,Rack-1,75,Under,3,7,7,0,60,86</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>BLK-029,backup_data.parquet,10240,128,80,3,NN-01,DN-06,Rack-2,SSD,58,415,310,18,26,640,Healthy,Rack-2,85,OK,0,0,0,0,60,86</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>BLK-030,backup_data.parquet,10240,128,80,3,NN-01,DN-10,Rack-3,HDD,75,210,160,45,58,640,Healthy,Rack-3,79,OK,0,0,0,0,60,86</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is HDFS (Hadoop Distributed File System)? Explain its core architecture using the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze NameNode, DataNode, Block structure | HDFS has NameNode (metadata) and DataNodes (data storage). Files split into 128MB blocks, replicated across DataNodes</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>HDFS provides distributed, fault-tolerant storage for Big Data</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is the default block size in HDFS? Why is 128MB used? Calculate total blocks from dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Block_Size_MB, Block_Count | Default block size: 128MB. Total blocks: 384 across all files. Large blocks reduce metadata overhead and improve throughput</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Large block size minimizes NameNode memory usage and improves sequential I/O</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is data replication in HDFS? Why is replication factor 3 used? Calculate storage overhead.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Replication_Factor, File_Size_MB | Replication factor: 3. Total raw data: 34,816 MB; Actual storage: 104,448 MB (3x overhead). Provides fault tolerance</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Replication ensures data durability - if one node fails, data available on 2 others</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is the role of NameNode in HDFS? Analyze NameNode metrics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Analyze NameNode_ID, Metadata_Size_KB | NameNode (NN-01) manages metadata: stores file-to-block mapping. Metadata size: 8-640 KB per file. Tracks block locations</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>NameNode is the master node - stores metadata, not actual data</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is the role of DataNode in HDFS? Analyze DataNode distribution and storage types.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze DataNode_ID, Storage_Type, Disk_Usage_Pct | DataNodes: DN-01 to DN-12 across 3 racks. Storage: SSD (45% usage, 48% avg) and HDD (68% usage, 58% avg)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>DataNodes store actual data blocks and report to NameNode</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is rack awareness in HDFS? How does it improve data locality?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Rack_ID, Data_Locality_Score | 3 racks (Rack-1,2,3). Data locality scores: 92-96 for local reads, 78-84 for remote. Rack awareness reduces cross-rack traffic</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Rack awareness places replicas across racks to prevent rack failure from causing data loss</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between SSD and HDD storage in HDFS? Compare performance metrics.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Compare SSD vs HDD performance metrics | SSD: Read 450-510 MBps, Write 350-390 MBps, Latency 8-18ms; HDD: Read 195-310 MBps, Write 140-240 MBps, Latency 24-72ms</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>SSD provides 2-3x faster performance for hot data; HDD for cold storage</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What is data locality? Calculate the data locality score for different file types.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Data_Locality_Score by file type | Customer data: 95, Product catalog: 96, User logs: 92, Sensor data: 80-88, Financial: 78-87. Larger files have lower locality</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Data locality improves performance by moving computation to data</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is block corruption in HDFS? Identify files with corrupt blocks.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Filter Corrupt_Blocks &gt; 0 | Financial transactions: 2 corrupt blocks; Backup data: 3 corrupt blocks; Sensor data: 1 corrupt block. Total: 6 corrupt blocks</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>HDFS automatically detects and replicates corrupt blocks</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What are under-replicated blocks? Identify files with replication issues.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Under_Replicated, Replication_Status | Clickstream: 2 under-replicated; Sensor data: 3; Financial: 5; Backup: 7. Total: 17 under-replicated blocks</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>HDFS automatically re-replicates under-replicated blocks to maintain replication factor</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is the HDFS balancer? Analyze the balancer score for different files.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Balancer_Score, Disk_Usage_Pct | Balancer scores: 85-90 for balanced files; 60-70 for unbalanced. Files with high disk usage (75-82%) have lower balancer scores</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Balancer redistributes data to ensure even cluster utilization</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between file size and read throughput? Analyze performance scaling.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Correlate File_Size_MB with Read_Throughput_MBps | Small files (128MB): 490 MBps; Medium (512MB): 310-420 MBps; Large (8192MB): 210-435 MBps. Larger files have more variable performance</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Performance depends on data distribution and storage type</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is the cluster health percentage? Calculate average health by storage type.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Group by Storage_Type; average Cluster_Health_Pct | SSD clusters: 97.8% health; HDD clusters: 93.2% health. Overall cluster health: 95.2%</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Regular monitoring and balancing maintain cluster health</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between read and write latency? Compare across storage types.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Compare Read_Latency_Ms vs Write_Latency_Ms | SSD: Read 8-16ms, Write 12-26ms; HDD: Read 24-55ms, Write 32-72ms. Write latency 30-40% higher than read</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Write operations require additional overhead for replication</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the HDFS architecture for large files? Analyze the 10GB backup file.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Analyze backup_data.parquet (10,240 MB) | Blocks: 80 blocks × 128MB; Replication: 3; Storage: 30,720 MB actual; Under-replicated: 7 blocks; Health: 86%</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Large files are split into many blocks distributed across cluster</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the NameNode metadata size? Calculate metadata overhead for different file sizes.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Analyze File_Size_MB vs Metadata_Size_KB | Small file (128MB): 8KB metadata; Large file (10GB): 640KB metadata. Overhead: ~64 bytes per block</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>NameNode memory limits number of files; each file/block consumes memory</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What are the different storage types used in HDFS? Identify files by storage type.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Group by Storage_Type, count files | SSD: 15 files (50%): user_logs, customer_data, weblogs, product_catalog; HDD: 15 files (50%): sales, clickstream, sensor, financial, backup</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Hot data on SSD, cold data on HDD for cost-performance balance</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is the replication status of files? Identify files with replication issues.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Replication_Status, Under_Replicated | OK: 24 files (80%); Under: 6 files (20%). Clickstream, sensor, financial, backup have under-replicated blocks</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Replication issues require attention to maintain fault tolerance</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What is the HDFS read and write throughput? Calculate average throughput by storage type.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Group by Storage_Type; average Read/Write Throughput | SSD: Read 475 MBps, Write 365 MBps; HDD: Read 255 MBps, Write 190 MBps. SSD is 1.9x faster</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Storage type selection impacts analytics performance</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>HDFS – Big Data Storage</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create an HDFS cluster summary with key metrics: total storage, used storage, replication overhead, cluster health.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Calculate summary metrics | Total Raw: 34,816 MB; Actual Storage: 104,448 MB (3x replication); Used: 62,669 MB (60%); Overhead: 69,632 MB; Health: 95.2%</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>HDFS provides scalable, fault-tolerant storage with replication overhead</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>